--- a/test/fixtures/files/mixed.xlsx
+++ b/test/fixtures/files/mixed.xlsx
@@ -489,16 +489,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>102</v>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Orin Thistle</t>
         </is>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>2</v>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0000000000002</t>
+        </is>
       </c>
       <c r="D5" s="0"/>
       <c r="E5" s="0" t="n">
@@ -522,16 +526,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="n">
-        <v>103</v>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Vela Reed</t>
         </is>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>3</v>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>0000000000003</t>
+        </is>
       </c>
       <c r="D6" s="0"/>
       <c r="E6" s="0" t="inlineStr">
@@ -553,8 +561,10 @@
           <t>Elo Moss</t>
         </is>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>4</v>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>0000000000004</t>
+        </is>
       </c>
       <c r="D7" s="0"/>
       <c r="E7" s="0" t="inlineStr">
@@ -588,16 +598,20 @@
       <c r="N8" s="0"/>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="n">
-        <v>105</v>
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Invalid Date Fiction</t>
         </is>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>5</v>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>0000000000005</t>
+        </is>
       </c>
       <c r="D9" s="0"/>
       <c r="E9" s="0" t="inlineStr">
@@ -612,16 +626,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="n">
-        <v>106</v>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Invalid Time Fiction</t>
         </is>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>6</v>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>0000000000006</t>
+        </is>
       </c>
       <c r="D10" s="0"/>
       <c r="E10" s="0" t="inlineStr">
@@ -636,8 +654,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="n">
-        <v>107</v>
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
       </c>
       <c r="B11" s="0"/>
       <c r="C11" s="0"/>
